--- a/content_forms/012_ai_ebook_creation_guide--content_forms.xlsx
+++ b/content_forms/012_ai_ebook_creation_guide--content_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -946,8 +946,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -975,12 +975,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'absolute_beginner',_'value':_'beginner'}</t>
+          <t>absolute_beginner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Absolute Beginner', 'value': 'beginner'}</t>
+          <t>Absolute Beginner</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'intermediate_/_enthusiast',_'value':_'intermediate'}</t>
+          <t>intermediate_/_enthusiast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Intermediate / Enthusiast', 'value': 'intermediate'}</t>
+          <t>Intermediate / Enthusiast</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'professional_/_expert',_'value':_'expert'}</t>
+          <t>professional_/_expert</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Professional / Expert', 'value': 'expert'}</t>
+          <t>Professional / Expert</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'lead_generation_(list_building)',_'value':_'lead_gen'}</t>
+          <t>lead_generation_(list_building)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Lead Generation (List building)', 'value': 'lead_gen'}</t>
+          <t>Lead Generation (List building)</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'educational_(course_companion)',_'value':_'educational'}</t>
+          <t>educational_(course_companion)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Educational (Course companion)', 'value': 'educational'}</t>
+          <t>Educational (Course companion)</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'authority_building_(thought_leadership)',_'value':_'authority'}</t>
+          <t>authority_building_(thought_leadership)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Authority Building (Thought leadership)', 'value': 'authority'}</t>
+          <t>Authority Building (Thought leadership)</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'direct_sales_(revenue_generation)',_'value':_'sales'}</t>
+          <t>direct_sales_(revenue_generation)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Direct Sales (Revenue generation)', 'value': 'sales'}</t>
+          <t>Direct Sales (Revenue generation)</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'formal_&amp;_academic',_'value':_'formal'}</t>
+          <t>formal_&amp;_academic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Formal &amp; Academic', 'value': 'formal'}</t>
+          <t>Formal &amp; Academic</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'conversational_&amp;_casual',_'value':_'conversational'}</t>
+          <t>conversational_&amp;_casual</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Conversational &amp; Casual', 'value': 'conversational'}</t>
+          <t>Conversational &amp; Casual</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'inspirational_&amp;_bold',_'value':_'inspirational'}</t>
+          <t>inspirational_&amp;_bold</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Inspirational &amp; Bold', 'value': 'inspirational'}</t>
+          <t>Inspirational &amp; Bold</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'technical_&amp;_precise',_'value':_'technical'}</t>
+          <t>technical_&amp;_precise</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Technical &amp; Precise', 'value': 'technical'}</t>
+          <t>Technical &amp; Precise</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'openai_(chatgpt/gpt-4)',_'value':_'openai'}</t>
+          <t>openai_(chatgpt/gpt-4)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'OpenAI (ChatGPT/GPT-4)', 'value': 'openai'}</t>
+          <t>OpenAI (ChatGPT/GPT-4)</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'anthropic_(claude)',_'value':_'anthropic'}</t>
+          <t>anthropic_(claude)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Anthropic (Claude)', 'value': 'anthropic'}</t>
+          <t>Anthropic (Claude)</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'midjourney_(illustrations)',_'value':_'midjourney'}</t>
+          <t>midjourney_(illustrations)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Midjourney (Illustrations)', 'value': 'midjourney'}</t>
+          <t>Midjourney (Illustrations)</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'jasper_/_copy.ai',_'value':_'jasper'}</t>
+          <t>jasper_/_copy.ai</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Jasper / Copy.ai', 'value': 'jasper'}</t>
+          <t>Jasper / Copy.ai</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'grammarly_/_prowritingaid',_'value':_'grammar_tools'}</t>
+          <t>grammarly_/_prowritingaid</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Grammarly / ProWritingAid', 'value': 'grammar_tools'}</t>
+          <t>Grammarly / ProWritingAid</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'ai-generated_illustrations',_'value':_'ai_images'}</t>
+          <t>ai-generated_illustrations</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'AI-Generated Illustrations', 'value': 'ai_images'}</t>
+          <t>AI-Generated Illustrations</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'stock_photography',_'value':_'stock_photos'}</t>
+          <t>stock_photography</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Stock Photography', 'value': 'stock_photos'}</t>
+          <t>Stock Photography</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'data_charts_&amp;_infographics',_'value':_'infographics'}</t>
+          <t>data_charts_&amp;_infographics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Data Charts &amp; Infographics', 'value': 'infographics'}</t>
+          <t>Data Charts &amp; Infographics</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'screenshots_/_tutorials',_'value':_'screenshots'}</t>
+          <t>screenshots_/_tutorials</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Screenshots / Tutorials', 'value': 'screenshots'}</t>
+          <t>Screenshots / Tutorials</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'pdf_(standard_layout)',_'value':_'pdf'}</t>
+          <t>pdf_(standard_layout)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'PDF (Standard Layout)', 'value': 'pdf'}</t>
+          <t>PDF (Standard Layout)</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'epub_(reflowable_text)',_'value':_'epub'}</t>
+          <t>epub_(reflowable_text)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'EPUB (Reflowable text)', 'value': 'epub'}</t>
+          <t>EPUB (Reflowable text)</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'mobi/kindle',_'value':_'mobi'}</t>
+          <t>mobi/kindle</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'MOBI/Kindle', 'value': 'mobi'}</t>
+          <t>MOBI/Kindle</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'google_doc_/_ms_word',_'value':_'docx'}</t>
+          <t>google_doc_/_ms_word</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Google Doc / MS Word', 'value': 'docx'}</t>
+          <t>Google Doc / MS Word</t>
         </is>
       </c>
     </row>
